--- a/real_estate_forms/002_home_loan_application--real_estate_forms.xlsx
+++ b/real_estate_forms/002_home_loan_application--real_estate_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -918,8 +918,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -947,12 +947,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'select_one',_'label':_'select_one',_'type':_'object',_'options':_[]}</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'select_one', 'label': 'Select One', 'type': 'object', 'options': []}</t>
+          <t>Select One</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'select_two',_'label':_'select_two',_'type':_'object',_'options':_[]}</t>
+          <t>select_two</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'select_two', 'label': 'Select Two', 'type': 'object', 'options': []}</t>
+          <t>Select Two</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'select_three',_'label':_'select_three',_'type':_'object',_'options':_[]}</t>
+          <t>select_three</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'select_three', 'label': 'Select Three', 'type': 'object', 'options': []}</t>
+          <t>Select Three</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'select_four',_'label':_'select_four',_'type':_'object',_'options':_[]}</t>
+          <t>select_four</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'select_four', 'label': 'Select Four', 'type': 'object', 'options': []}</t>
+          <t>Select Four</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'select_five',_'label':_'select_five',_'type':_'object',_'options':_[]}</t>
+          <t>select_five</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'select_five', 'label': 'Select Five', 'type': 'object', 'options': []}</t>
+          <t>Select Five</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'select_six',_'label':_'select_six',_'type':_'object',_'options':_[]}</t>
+          <t>select_six</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'select_six', 'label': 'Select Six', 'type': 'object', 'options': []}</t>
+          <t>Select Six</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'select_seven',_'label':_'select_seven',_'type':_'object',_'options':_[]}</t>
+          <t>select_seven</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'select_seven', 'label': 'Select Seven', 'type': 'object', 'options': []}</t>
+          <t>Select Seven</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'select_eight',_'label':_'select_eight',_'type':_'object',_'options':_[]}</t>
+          <t>select_eight</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'select_eight', 'label': 'Select Eight', 'type': 'object', 'options': []}</t>
+          <t>Select Eight</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'select_nine',_'label':_'select_nine',_'type':_'object',_'options':_[]}</t>
+          <t>select_nine</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'select_nine', 'label': 'Select Nine', 'type': 'object', 'options': []}</t>
+          <t>Select Nine</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'select_ten',_'label':_'select_ten',_'type':_'object',_'options':_[]}</t>
+          <t>select_ten</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'select_ten', 'label': 'Select Ten', 'type': 'object', 'options': []}</t>
+          <t>Select Ten</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'select_eleven',_'label':_'select_eleven',_'type':_'object',_'options':_[]}</t>
+          <t>select_eleven</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'select_eleven', 'label': 'Select Eleven', 'type': 'object', 'options': []}</t>
+          <t>Select Eleven</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'select_twelve',_'label':_'select_twelve',_'type':_'object',_'options':_[]}</t>
+          <t>select_twelve</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'select_twelve', 'label': 'Select Twelve', 'type': 'object', 'options': []}</t>
+          <t>Select Twelve</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'select_thirteen',_'label':_'select_thirteen',_'type':_'object',_'options':_[]}</t>
+          <t>select_thirteen</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'select_thirteen', 'label': 'Select Thirteen', 'type': 'object', 'options': []}</t>
+          <t>Select Thirteen</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'select_fourteen',_'label':_'select_fourteen',_'type':_'object',_'options':_[]}</t>
+          <t>select_fourteen</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'select_fourteen', 'label': 'Select Fourteen', 'type': 'object', 'options': []}</t>
+          <t>Select Fourteen</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'select_fifteen',_'label':_'select_fifteen',_'type':_'object',_'options':_[]}</t>
+          <t>select_fifteen</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'select_fifteen', 'label': 'Select Fifteen', 'type': 'object', 'options': []}</t>
+          <t>Select Fifteen</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'select_sixteen',_'label':_'select_sixteen',_'type':_'object',_'options':_[]}</t>
+          <t>select_sixteen</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'select_sixteen', 'label': 'Select Sixteen', 'type': 'object', 'options': []}</t>
+          <t>Select Sixteen</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'select_seventeen',_'label':_'select_seventeen',_'type':_'object',_'options':_[]}</t>
+          <t>select_seventeen</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'select_seventeen', 'label': 'Select Seventeen', 'type': 'object', 'options': []}</t>
+          <t>Select Seventeen</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'select_eighteen',_'label':_'select_eighteen',_'type':_'object',_'options':_[]}</t>
+          <t>select_eighteen</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'select_eighteen', 'label': 'Select Eighteen', 'type': 'object', 'options': []}</t>
+          <t>Select Eighteen</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'select_nineteen',_'label':_'select_nineteen',_'type':_'object',_'options':_[]}</t>
+          <t>select_nineteen</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'select_nineteen', 'label': 'Select Nineteen', 'type': 'object', 'options': []}</t>
+          <t>Select Nineteen</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'select_twenty',_'label':_'select_twenty',_'type':_'object',_'options':_[]}</t>
+          <t>select_twenty</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'select_twenty', 'label': 'Select Twenty', 'type': 'object', 'options': []}</t>
+          <t>Select Twenty</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'select_twentyone',_'label':_'select_twenty_one',_'type':_'object',_'options':_[]}</t>
+          <t>select_twenty_one</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'select_twentyone', 'label': 'Select Twenty One', 'type': 'object', 'options': []}</t>
+          <t>Select Twenty One</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'select_twentytwo',_'label':_'select_twenty_two',_'type':_'object',_'options':_[]}</t>
+          <t>select_twenty_two</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'select_twentytwo', 'label': 'Select Twenty Two', 'type': 'object', 'options': []}</t>
+          <t>Select Twenty Two</t>
         </is>
       </c>
     </row>
